--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:35</t>
+    <t xml:space="preserve">2026-09-10 00:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2023_o higgins.xlsx
@@ -87,6 +87,9 @@
     <t xml:space="preserve">Peumo</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:43</t>
+    <t xml:space="preserve">2026-09-18 10:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6302</v>
+        <v>6204</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>57.33</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="20">
@@ -880,13 +880,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6202</v>
+        <v>6302</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>56.78</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6109</v>
+        <v>6202</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>56.49</v>
+        <v>56.78</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6303</v>
+        <v>6109</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>56.12</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="23">
@@ -931,13 +931,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6104</v>
+        <v>6303</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>55.33</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6206</v>
+        <v>6104</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>54.86</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6309</v>
+        <v>6206</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>53.78</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6306</v>
+        <v>6309</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>52.14</v>
+        <v>53.78</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6205</v>
+        <v>6306</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>51.88</v>
+        <v>52.14</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6308</v>
+        <v>6205</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>51.4</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>50.59</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6107</v>
+        <v>6305</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>50.43</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6113</v>
+        <v>6107</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>50.26</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6203</v>
+        <v>6113</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>50.2</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6304</v>
+        <v>6203</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>47.42</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6304</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>47.42</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>
